--- a/sources/kunimitsu_step8b.xlsx
+++ b/sources/kunimitsu_step8b.xlsx
@@ -423,7 +423,7 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -943,27 +943,27 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>1+3 [tag]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1+3 [tag]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2+4 [tag]; 2+5 [tag]</t>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tornado [Tag]</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tornado [Tag]</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -994,6 +994,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>Only does 20 damage if you tag.</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">

--- a/sources/kunimitsu_step8b.xlsx
+++ b/sources/kunimitsu_step8b.xlsx
@@ -929,6 +929,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>30789c48-adc1-43a6-8721-635dee152db2</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>30789c48-adc1-43a6-8721-635dee152db2</t>
@@ -1001,6 +1006,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
@@ -1061,6 +1071,11 @@
       <c r="V9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>66c176e2-e46f-45a2-84bf-6b63c3ac4a23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -7357,6 +7372,11 @@
       <c r="T84" t="inlineStr">
         <is>
           <t>hmm"h"h"Lmhm"!</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>de1828d4-6182-4a4b-8d22-85b48de701af</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">

--- a/sources/kunimitsu_step8b.xlsx
+++ b/sources/kunimitsu_step8b.xlsx
@@ -417,38 +417,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AD84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col hidden="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col hidden="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col hidden="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col hidden="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="113" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col hidden="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col hidden="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="113" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,125 +482,130 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -616,57 +622,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Leaping Body Slam</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Leaping Body Slam</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>d16e0137-d344-4c32-b554-95a38da219c0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>c8d042d3-bbfb-429c-b880-25bf37fc1f47</t>
         </is>
@@ -683,57 +689,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Sickle Bash</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Sickle Bash</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>934774ee-46d3-4245-bea2-4c0382970f7b</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>799b9426-e3ff-4d4d-bda3-264f994f01a0</t>
         </is>
@@ -750,57 +756,57 @@
           <t>db+1+3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Judo Hip Toss</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Judo Hip Toss</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>4c0c6d79-b1f9-41d4-b7c8-075edfd9d053</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>da250dd4-03fc-4209-b5b8-dacdcf118ab8</t>
         </is>
@@ -817,62 +823,62 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Manji Rana</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Manji Rana</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>d/f</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>The first part can't be escaped, but you can avoid the actual throw after the air flip.</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>948e06cd-7bbc-4a5c-985e-ae278ef1f616</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>1fb01f38-90db-4c8a-8e33-a2a72b14db44</t>
         </is>
@@ -896,50 +902,55 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>30789c48-adc1-43a6-8721-635dee152db2</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>30789c48-adc1-43a6-8721-635dee152db2</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -963,60 +974,65 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Tornado</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Tornado</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>40_20</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>4020</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>40_20</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Only does 20 damage if you tag.</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1040,50 +1056,55 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Reverse Neck Toss</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Reverse Neck Toss</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>66c176e2-e46f-45a2-84bf-6b63c3ac4a23</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>66c176e2-e46f-45a2-84bf-6b63c3ac4a23</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1120,125 +1141,130 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="O12" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="P12" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P12" s="1" t="inlineStr">
+      <c r="Q12" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q12" s="1" t="inlineStr">
+      <c r="R12" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R12" s="1" t="inlineStr">
+      <c r="S12" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S12" s="1" t="inlineStr">
+      <c r="T12" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T12" s="1" t="inlineStr">
+      <c r="U12" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U12" s="1" t="inlineStr">
+      <c r="V12" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V12" s="1" t="inlineStr">
+      <c r="W12" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W12" s="1" t="inlineStr">
+      <c r="X12" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X12" s="1" t="inlineStr">
+      <c r="Y12" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AA12" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr">
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB12" s="1" t="inlineStr">
+      <c r="AC12" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC12" s="1" t="inlineStr">
+      <c r="AD12" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1255,77 +1281,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>a9492a47-77cd-46c1-bb80-07a2a4ea0012</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>189eed81-b605-46e8-ad71-b210ddc38dc7</t>
         </is>
@@ -1342,77 +1368,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>c9113be0-f327-400a-8edc-5f0d5e300570</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>d02fed34-2e82-4140-9b1b-a472dae43a45</t>
         </is>
@@ -1429,31 +1455,26 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1471,35 +1492,40 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>08b0712a-8948-457f-a270-78e435b10bd0</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>ef82b352-ae86-4046-8fa1-1df8e8deda2d</t>
         </is>
@@ -1516,77 +1542,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>d1eba530-e47a-4179-beb3-1edc8f739523</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>bbcd2d46-32e8-40f3-99a7-759e3d9a58df</t>
         </is>
@@ -1603,77 +1629,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>2b9739b2-8c50-49fd-9c69-89692af415a8</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>e5ffeda5-b32b-4ed1-9b94-9f37cbfd60f6</t>
         </is>
@@ -1690,77 +1716,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>285012eb-db69-4c31-92f7-d080e4704bf0</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>2623a165-6c14-4d65-b805-b29f3f251bea</t>
         </is>
@@ -1777,31 +1803,26 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1819,35 +1840,40 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>0439a740-fe1e-4f3e-9b02-73681643ca92</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>8b27b11c-b066-4589-bd89-dc558b18abe6</t>
         </is>
@@ -1864,41 +1890,36 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1906,35 +1927,40 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>17334e42-f473-4b47-89cd-0b6337d02817</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>41de2df8-7151-4924-96be-086ffb0f2f59</t>
         </is>
@@ -1951,77 +1977,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>9705b93b-2590-4aa2-9960-0a25747ad512</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>588c7cb3-b254-4ea4-88dc-fa95d3f295f2</t>
         </is>
@@ -2038,77 +2064,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>dfb242e5-22f0-4960-b1f1-923073d4decf</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>3d17f22d-5944-4a22-b541-7a547a196d7e</t>
         </is>
@@ -2125,77 +2151,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>31289e8c-8120-421d-b817-67ea5672dce9</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>f761b67d-4b04-4a74-bedc-77506f6b119e</t>
         </is>
@@ -2212,77 +2238,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>2fd1b492-9aa2-4bc4-b6ea-50d80cc9ef0f</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>a1362a1d-13e9-4916-9029-8d946b25a93c</t>
         </is>
@@ -2299,77 +2325,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>28fb7a45-2513-4117-b386-c6e837211094</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>c6a7c5e8-c924-410b-ae08-7fd2e6850c67</t>
         </is>
@@ -2386,77 +2412,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>10feec0a-578d-4844-ba47-ac32d4f8a584</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>1f4dd564-e5f8-4f06-afe7-6edd1576ce4a</t>
         </is>
@@ -2473,77 +2499,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>9cfae40f-5b10-4463-8e57-a8ad074c11ac</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>721d874a-ce3a-42d6-9d57-c239f306c351</t>
         </is>
@@ -2560,77 +2586,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>475579bf-a359-48a8-ad82-35eccd76c4ed</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>56525003-2766-4cb2-b277-26fb034ef917</t>
         </is>
@@ -2647,77 +2673,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>e0bce670-2f40-4e7b-aa46-28b886229ed9</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>9f96e90a-61eb-4a13-881d-a393d042513f</t>
         </is>
@@ -2734,77 +2760,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>f8cc8067-5ec2-46b7-a8e7-51dafe29be43</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>76dcd55a-4951-4ad7-8d6e-89a2e43116f9</t>
         </is>
@@ -2821,31 +2847,26 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>KD</t>
@@ -2863,35 +2884,40 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>f2a5e18a-f435-47bb-8cb9-3f2047c6511f</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>a7faaa92-a092-4afe-95d7-7044573c1851</t>
         </is>
@@ -2908,77 +2934,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>f2b07176-a0b9-42e1-abd8-8935084e4ac2</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>8ffe075d-1d75-425e-91d5-f51c664e24f8</t>
         </is>
@@ -2995,77 +3021,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>6d72a15a-a4ab-4580-9b6b-c205967f39c5</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>03bb952e-687c-45f7-86b4-9e8dde987cd3</t>
         </is>
@@ -3082,31 +3108,26 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3124,35 +3145,40 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>0d4c5f1c-0b72-4d40-8e69-e9a8a5488867</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>a71acb70-5603-457d-96e8-c6b3484df21c</t>
         </is>
@@ -3169,77 +3195,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>c67b4933-e913-41e3-92e3-112d49de4317</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>33162c24-23ee-470e-ab82-95fa167dd3ba</t>
         </is>
@@ -3256,77 +3282,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>7f0e8b5d-823d-4930-a964-4014dac709a3</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>9046fa61-4179-4f87-af90-ccc2c6801ac2</t>
         </is>
@@ -3363,125 +3389,130 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="I39" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="K39" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K39" s="1" t="inlineStr">
+      <c r="L39" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
+      <c r="M39" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M39" s="1" t="inlineStr">
+      <c r="N39" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
+      <c r="O39" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O39" s="1" t="inlineStr">
+      <c r="P39" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P39" s="1" t="inlineStr">
+      <c r="Q39" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q39" s="1" t="inlineStr">
+      <c r="R39" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R39" s="1" t="inlineStr">
+      <c r="S39" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S39" s="1" t="inlineStr">
+      <c r="T39" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T39" s="1" t="inlineStr">
+      <c r="U39" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U39" s="1" t="inlineStr">
+      <c r="V39" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V39" s="1" t="inlineStr">
+      <c r="W39" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W39" s="1" t="inlineStr">
+      <c r="X39" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X39" s="1" t="inlineStr">
+      <c r="Y39" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="inlineStr">
+      <c r="Z39" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
+      <c r="AA39" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA39" s="1" t="inlineStr">
+      <c r="AB39" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB39" s="1" t="inlineStr">
+      <c r="AC39" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC39" s="1" t="inlineStr">
+      <c r="AD39" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3498,87 +3529,87 @@
           <t>1,2,1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Jab - Double Uppercut</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Jab - Double Uppercut</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>+2 -13 -12</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>+2 -13 -12</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+7 -2 -1</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+7 -2 -1</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+7 -2 -1</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>+7 -2 -1</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>5,8,6</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>5,8,6</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>1ad3e644-0910-4b82-b570-a929b5f078dd</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>832762de-a678-44ac-acde-dab8b577ce3a</t>
         </is>
@@ -3595,92 +3626,92 @@
           <t>b+1,1,1,1,1,1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Stone Fists</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Stone Fists</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>17 x x x x x</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>17 x x x x x</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>+1 +6 +6 +6 +6 +6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>+1 +6 +6 +6 +6 +6</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+12 +7 +7 +7 +7 x</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+12 +7 +7 +7 +7 x</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+12 +7 +7 +7 +7 x</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>+12 +7 +7 +7 +7 x</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>10,10,10,10,10,10</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>10,10,10,10,10,10</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>hhhhhh</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>hhhhhh</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>On the 6th spin Kunimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>ca0deef3-f459-4a09-b007-fc4c2a5f994a</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>b74bc4f5-52f5-498b-b32d-1b843a9fdc9b</t>
         </is>
@@ -3697,41 +3728,36 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Kunai Thrust</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Kunai Thrust</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3749,35 +3775,40 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>269afa86-6f4a-45d9-bdab-cc5e9019183d</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>86a323c7-dd35-444d-9c50-2cd25f8517e0</t>
         </is>
@@ -3794,92 +3825,92 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Dive Bomb</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Dive Bomb</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>adbd1045-7a73-4e64-bd6c-a0dce5c28f2d</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>2d132bae-a2e1-4311-a76e-ba44d1224fef</t>
         </is>
@@ -3896,41 +3927,36 @@
           <t>SS+1+2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Winter Wind</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Winter Wind</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3948,35 +3974,40 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>f352867b-a19e-422b-b973-a1b199ed8f4a</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>a30f96ad-70bc-48b0-9f16-1372554852b0</t>
         </is>
@@ -3993,41 +4024,36 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Cycle of Rebirth</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Cycle of Rebirth</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-41</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-41</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4045,35 +4071,40 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>8,11</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>8,11</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>h!</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>h!</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>8733de27-98b4-47e8-9948-ca3df7416d50</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>35f2e59e-eca6-499c-8462-dc861abf3952</t>
         </is>
@@ -4090,92 +4121,92 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Backfist</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Backfist</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>2903fc78-5206-42e6-b99f-352be67815ee</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>8de1ad39-c19b-43e8-8dfe-bd9a7465f0fe</t>
         </is>
@@ -4197,92 +4228,92 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Backfist</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Backfist</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>+17</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>d3dcd0a7-a3e5-4310-8c58-759e6118f1b2</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>578244c3-f6dc-4f6c-aba4-e93b93272661</t>
         </is>
@@ -4299,62 +4330,62 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Step In Upper</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Step In Upper</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>JG JGcco</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Will only hit crouching opponents at the correct range.</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>af8e63a9-4b8e-48a2-8616-5ca50d9c8780</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>55796929-3a6b-405a-80ba-b1d28f9f913a</t>
         </is>
@@ -4371,87 +4402,87 @@
           <t>2,3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Flash Attack</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Flash Attack</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0 -12</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>0 -12</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>+6 KD</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>ca44f631-c896-4051-8dce-79dffeb245d8</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>df4f4b09-d41d-4e61-ae6e-d8f471aad4ae</t>
         </is>
@@ -4468,92 +4499,92 @@
           <t>2,d+3</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Low Flash Attack</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Low Flash Attack</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>0 -15</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>+6 -1</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>12,8</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>12,8</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>8b838f63-2726-459a-8f2e-c2612b1f5eef</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>6de4e8ee-8b62-469f-94f4-bbc8f9233982</t>
         </is>
@@ -4570,41 +4601,36 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Rising Kuzura</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Rising Kuzura</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4622,45 +4648,50 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>f945ff21-aa11-4726-ab60-04abfad8ded7</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>0fe18478-03b9-460e-90e7-425b5e7de0f8</t>
         </is>
@@ -4677,47 +4708,47 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Inverted Stalker</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Inverted Stalker</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>95b461a9-e530-4480-816a-5d7517a68c98</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>85eac39f-46eb-4169-904b-bcc383277cea</t>
         </is>
@@ -4734,36 +4765,31 @@
           <t>f,f+3,4</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>– Thrust Stalker</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Inverted Stalker – Thrust Stalker</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4781,45 +4807,50 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>-,30</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>4bbde7f2-7131-4359-84bb-be9e1f058222</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>7facffd9-6e73-4e25-af51-4ebaadc79965</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>95b461a9-e530-4480-816a-5d7517a68c98</t>
         </is>
@@ -4836,87 +4867,87 @@
           <t>3,4</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Zig Zag</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Zig Zag</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-8 -14</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-8 -14</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>30,30</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>30,30</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>8f125e92-0a87-4459-a1c9-02102a365ad3</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>9de3bf02-378e-4e6d-8543-ef5e8041143d</t>
         </is>
@@ -4938,46 +4969,41 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Ninja Jewel</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Ninja Jewel</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4995,40 +5021,45 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>f89f3617-7c3c-43d0-a9c0-d61fc89b6956</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>d17b6646-61fb-44eb-bb50-90e1d138c4a2</t>
         </is>
@@ -5045,41 +5076,36 @@
           <t>FC+df+3</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Lunging Sweep</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Lunging Sweep</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5097,40 +5123,45 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>JG RC BS</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>eb48fb28-125a-4f1a-b669-0bd7b7d3e3f8</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>e3d2b045-b371-4df1-87df-9df825af50cf</t>
         </is>
@@ -5147,97 +5178,97 @@
           <t>DB+3,3,3,3,3,3</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Manji Spin Kicks</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Manji Spin Kicks</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-24 -23 -23 -23 -23</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-24 -23 -23 -23 -23</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>-13 -11 -11 -11 -11</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>-13 -11 -11 -11 -11</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>-13 -11 -11 -11 -11</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>-13 -11 -11 -11 -11</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>12,7,7,5,5,5</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>12,7,7,5,5,5</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>Llllll</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>Llllll</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>On the 6th spin Kunimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>dd8c1a6c-c042-46f9-a819-0252d0ff4a93</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>166fad3c-a879-4735-bf90-3678ca9586f2</t>
         </is>
@@ -5254,92 +5285,92 @@
           <t>DB+3,3,3,3,3,3,f+4</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>– Rising Kick</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Manji Spin Kicks – Rising Kick</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-24 -23 -23 -23 -23 -4</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M58" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
           <t>-13 -11 -11 -11 -11 KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O58" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
           <t>-13 -11 -11 -11 -11 KD</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>12,7,7,5,5,5,12</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>Llllllm</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Rising Kick can be done after any kick but the last.</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>bb4f6de0-752e-476b-81ca-b3fb8181b921</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>67e88882-9c22-4160-ac16-21b91c1588b1</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>dd8c1a6c-c042-46f9-a819-0252d0ff4a93</t>
         </is>
@@ -5356,41 +5387,36 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Poison Wind</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Poison Wind</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5408,35 +5434,40 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>dc722b85-6780-4680-9ab8-92a834484433</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>9c9cbcaf-ce0d-40d2-bcb7-f520ef54b465</t>
         </is>
@@ -5453,87 +5484,87 @@
           <t>f,f+3+4</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Shark Attack</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Shark Attack</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>89d66450-2538-4fe2-a1a7-0698b0b7a13d</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>ca0bee59-8f75-42b0-9517-3ad408f527c1</t>
         </is>
@@ -5550,87 +5581,87 @@
           <t>f,f+3+4,1+2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>– Dive Bomb</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Shark Attack – Dive Bomb</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-20 -27</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>-9 KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O61" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
           <t>-9 KD</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>30,40</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>7973d799-9407-41ee-9db9-7ef4af16517d</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>0c8daba6-c614-4ebb-b2fb-43212c5f1030</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>89d66450-2538-4fe2-a1a7-0698b0b7a13d</t>
         </is>
@@ -5647,97 +5678,97 @@
           <t>f,f+3+4~3</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>– Ninja Jewel</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Shark Attack – Ninja Jewel</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-20 0</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
           <t>-9 KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O62" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
           <t>-9 KD</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>30,25</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>You are not BT if the move hits a regular sized standing opponent. It whiffs regular sized crouching opponents.</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>5f0275c7-8f26-41e7-852d-12aa3e6a6f80</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>24483cbc-1163-45dd-94fe-281db5ab7948</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>89d66450-2538-4fe2-a1a7-0698b0b7a13d</t>
         </is>
@@ -5754,92 +5785,92 @@
           <t>f,f+3+4,3+4</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>– Ninja Flying Shadow</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Shark Attack – Ninja Flying Shadow</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-20 x</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>-9 x</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>-9 x</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>30,-</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Kunimitsu ends up behind the opponent.</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>8a1ad63b-42ee-441a-b7b5-264e038664f8</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>48025fc3-b15b-4c18-97d0-927a756682ba</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>89d66450-2538-4fe2-a1a7-0698b0b7a13d</t>
         </is>
@@ -5863,39 +5894,39 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>d+3+4</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Fairy Wax</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Fairy Wax</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5913,35 +5944,40 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
           <t>5,23</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>5,23</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>Mm</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>Mm</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>42f9d48b-06c0-4659-94ab-897f2757e851</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>4281b6c4-78bc-4967-8977-1e864c2d9230</t>
         </is>
@@ -5958,41 +5994,36 @@
           <t>SS+3+4</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Kunai Dragon Tail</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Kunai Dragon Tail</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-37</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-37</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6010,40 +6041,45 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>RC BS</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>32401282-dd83-4f9b-a4e4-45a26202b0c6</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>ecbe9cdc-7b7f-493f-b779-dba94d11ed9c</t>
         </is>
@@ -6060,41 +6096,36 @@
           <t>f+3+4</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Growling Jewel</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Growling Jewel</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6112,35 +6143,40 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>e867ac6d-6979-4fdf-b749-16d80d53f5ed</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>080cdaf8-7bd0-4ab0-b921-c5dc023daca0</t>
         </is>
@@ -6157,41 +6193,36 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Fubuki</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Fubuki</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6209,35 +6240,40 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>41e4fd4e-9384-4766-a438-9c41495f8770</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>26c8cc40-c149-44d5-b454-2ffc5795bfea</t>
         </is>
@@ -6254,92 +6290,92 @@
           <t>4,4,4</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Triple Roundhouse</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Triple Roundhouse</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-14 -5 -8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-14 -5 -8</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-3 -3 -4</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-3 -3 -4</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>-3 -3 -4</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>-3 -3 -4</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>20,20,21</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>20,20,21</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>OB GB</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>5022d49f-2e6f-4aeb-9aaf-f08d8aefe8cd</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>8f73322f-1b61-4658-a5e9-aa3edb440d4c</t>
         </is>
@@ -6363,45 +6399,50 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>u+4; uf+4</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>Avoiding the Puddle</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Avoiding the Puddle</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>0100b8e3-d10c-4ce8-a865-5ffd20d3e224</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>6560ebc4-c7d7-416e-b97e-bd1f6d47ec94</t>
         </is>
@@ -6418,47 +6459,47 @@
           <t>uf,N+4</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Hop Spin</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Hop Spin</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>7312f2f6-2965-4cee-afbf-bfaaa4299ece</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>bee15a8d-97b8-441d-8611-263ee5775a9e</t>
         </is>
@@ -6475,52 +6516,52 @@
           <t>d+1+2</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Earth Divide</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Earth Divide</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>Avoids all attacks.</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>8d607cf6-6bcc-4d77-987c-4ba110afd2aa</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>0000671f-3ae9-4ac3-b1c0-179b23e5341b</t>
         </is>
@@ -6537,47 +6578,47 @@
           <t>u,ub</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Evasive Backflip</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Evasive Backflip</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>cc9fe5a6-d4e2-4971-95c6-581190eb85d0</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>4081b28f-5420-47c4-a860-7c2a1d7b4fd6</t>
         </is>
@@ -6614,125 +6655,130 @@
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
+      <c r="H75" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H75" s="1" t="inlineStr">
+      <c r="I75" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I75" s="1" t="inlineStr">
+      <c r="J75" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J75" s="1" t="inlineStr">
+      <c r="K75" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K75" s="1" t="inlineStr">
+      <c r="L75" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L75" s="1" t="inlineStr">
+      <c r="M75" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M75" s="1" t="inlineStr">
+      <c r="N75" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N75" s="1" t="inlineStr">
+      <c r="O75" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O75" s="1" t="inlineStr">
+      <c r="P75" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P75" s="1" t="inlineStr">
+      <c r="Q75" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q75" s="1" t="inlineStr">
+      <c r="R75" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R75" s="1" t="inlineStr">
+      <c r="S75" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S75" s="1" t="inlineStr">
+      <c r="T75" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T75" s="1" t="inlineStr">
+      <c r="U75" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U75" s="1" t="inlineStr">
+      <c r="V75" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V75" s="1" t="inlineStr">
+      <c r="W75" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W75" s="1" t="inlineStr">
+      <c r="X75" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X75" s="1" t="inlineStr">
+      <c r="Y75" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y75" s="1" t="inlineStr">
+      <c r="Z75" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z75" s="1" t="inlineStr">
+      <c r="AA75" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA75" s="1" t="inlineStr">
+      <c r="AB75" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB75" s="1" t="inlineStr">
+      <c r="AC75" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC75" s="1" t="inlineStr">
+      <c r="AD75" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -6749,77 +6795,77 @@
           <t>db+2</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Kunai Stab</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Kunai Stab</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>706385cc-db8f-472c-a5d8-a4727563f7f1</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>abe84b61-a2f1-4ab6-b90a-a8928bed3ce0</t>
         </is>
@@ -6836,31 +6882,26 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Kunai Murder</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Kunai Murder</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6878,35 +6919,40 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>a40f6bee-707a-4b6b-bb62-fa1151f2046f</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>e84319a7-c5fd-471d-b97b-2db790b04e7d</t>
         </is>
@@ -6923,31 +6969,26 @@
           <t>f,f,N+2</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Kunai Advance</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Kunai Advance</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6965,35 +7006,40 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>f8a6ab30-147e-4948-a27b-a95308d6b34a</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>22239015-c188-4d11-a6fc-a976dd2c7b61</t>
         </is>
@@ -7010,41 +7056,36 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Cycle of Rebirth</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Cycle of Rebirth</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-41</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-41</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7062,35 +7103,40 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
           <t>8,11</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>8,11</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>h!</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>h!</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>1761f62d-a297-48ec-ae07-3c605c2ebd35</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>f49d5d95-52aa-4565-8178-e4ad7b879687</t>
         </is>
@@ -7107,31 +7153,26 @@
           <t>u+1+2</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Kunai Sky Drop</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Kunai Sky Drop</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7149,35 +7190,40 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>44b87bb6-4383-45c3-b2da-78bf894ec3d6</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>95822dd7-a897-4cd5-95a2-7001fd7d0d03</t>
         </is>
@@ -7214,125 +7260,130 @@
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
+      <c r="G83" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
+      <c r="H83" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H83" s="1" t="inlineStr">
+      <c r="I83" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I83" s="1" t="inlineStr">
+      <c r="J83" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J83" s="1" t="inlineStr">
+      <c r="K83" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K83" s="1" t="inlineStr">
+      <c r="L83" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L83" s="1" t="inlineStr">
+      <c r="M83" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M83" s="1" t="inlineStr">
+      <c r="N83" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N83" s="1" t="inlineStr">
+      <c r="O83" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O83" s="1" t="inlineStr">
+      <c r="P83" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P83" s="1" t="inlineStr">
+      <c r="Q83" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q83" s="1" t="inlineStr">
+      <c r="R83" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R83" s="1" t="inlineStr">
+      <c r="S83" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S83" s="1" t="inlineStr">
+      <c r="T83" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T83" s="1" t="inlineStr">
+      <c r="U83" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U83" s="1" t="inlineStr">
+      <c r="V83" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V83" s="1" t="inlineStr">
+      <c r="W83" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W83" s="1" t="inlineStr">
+      <c r="X83" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X83" s="1" t="inlineStr">
+      <c r="Y83" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y83" s="1" t="inlineStr">
+      <c r="Z83" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z83" s="1" t="inlineStr">
+      <c r="AA83" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA83" s="1" t="inlineStr">
+      <c r="AB83" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB83" s="1" t="inlineStr">
+      <c r="AC83" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC83" s="1" t="inlineStr">
+      <c r="AD83" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7349,42 +7400,42 @@
           <t>1,2,1,4,4,4,1,2,3,2</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>5,8,6,9,9,5,5,7,12,25</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>5,8,6,9,9,5,5,7,12,25</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>hmm"h"h"Lmhm"!</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>hmm"h"h"Lmhm"!</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>de1828d4-6182-4a4b-8d22-85b48de701af</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>de1828d4-6182-4a4b-8d22-85b48de701af</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
+      <c r="AD84" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
